--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1514"/>
+  <dimension ref="A1:C1515"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17044,6 +17044,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1515" spans="1:3">
+      <c r="A1515" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B1515">
+        <v>110480</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -17049,7 +17049,7 @@
         <v>46267</v>
       </c>
       <c r="B1515">
-        <v>110480</v>
+        <v>108750</v>
       </c>
       <c r="C1515" t="s">
         <v>3</v>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1515"/>
+  <dimension ref="A1:C1516"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17055,6 +17055,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1516" spans="1:3">
+      <c r="A1516" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B1516">
+        <v>108750</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1516"/>
+  <dimension ref="A1:C1517"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17066,6 +17066,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1517" spans="1:3">
+      <c r="A1517" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B1517">
+        <v>109340</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -17071,7 +17071,7 @@
         <v>46269</v>
       </c>
       <c r="B1517">
-        <v>109340</v>
+        <v>109945</v>
       </c>
       <c r="C1517" t="s">
         <v>3</v>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1517"/>
+  <dimension ref="A1:C1518"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17077,6 +17077,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1518" spans="1:3">
+      <c r="A1518" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B1518">
+        <v>109945</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1518"/>
+  <dimension ref="A1:C1519"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17088,6 +17088,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1519" spans="1:3">
+      <c r="A1519" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B1519">
+        <v>109900</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1519"/>
+  <dimension ref="A1:C1520"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17099,6 +17099,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1520" spans="1:3">
+      <c r="A1520" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B1520">
+        <v>111290</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1520"/>
+  <dimension ref="A1:C1521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17110,6 +17110,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1521" spans="1:3">
+      <c r="A1521" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B1521">
+        <v>111525</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1521"/>
+  <dimension ref="A1:C1522"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17121,6 +17121,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1522" spans="1:3">
+      <c r="A1522" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B1522">
+        <v>112490</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1522"/>
+  <dimension ref="A1:C1523"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17132,6 +17132,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1523" spans="1:3">
+      <c r="A1523" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B1523">
+        <v>109310</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
